--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3149,6 +3149,336 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125920143</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>448215</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6987268</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>125920942</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>448197</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6987113</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>125920350</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>448494</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6987154</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Oviken</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Tomas Wiltén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3040,10 +3040,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125902826</v>
+        <v>125920942</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3051,37 +3051,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BERG DÖRRSÅDALEN 1:2, Gräftåvallen, Oviken, Jmt</t>
+          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448621</v>
+        <v>448197</v>
       </c>
       <c r="R22" t="n">
-        <v>6987672</v>
+        <v>6987113</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3111,19 +3116,14 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:00</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3132,7 +3132,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3261,7 +3260,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125920942</v>
+        <v>125920350</v>
       </c>
       <c r="B24" t="n">
         <v>57651</v>
@@ -3304,10 +3303,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448197</v>
+        <v>448494</v>
       </c>
       <c r="R24" t="n">
-        <v>6987113</v>
+        <v>6987154</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3371,10 +3370,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125920350</v>
+        <v>125902826</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3382,42 +3381,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
+          <t>BERG DÖRRSÅDALEN 1:2, Gräftåvallen, Oviken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448494</v>
+        <v>448621</v>
       </c>
       <c r="R25" t="n">
-        <v>6987154</v>
+        <v>6987672</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3452,17 +3446,13 @@
           <t>2025-06-10</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3373,7 +3373,7 @@
         <v>125902826</v>
       </c>
       <c r="B25" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3040,7 +3040,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920942</v>
+        <v>125920143</v>
       </c>
       <c r="B22" t="n">
         <v>57651</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448197</v>
+        <v>448215</v>
       </c>
       <c r="R22" t="n">
-        <v>6987113</v>
+        <v>6987268</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125920143</v>
+        <v>125920942</v>
       </c>
       <c r="B23" t="n">
         <v>57651</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448215</v>
+        <v>448197</v>
       </c>
       <c r="R23" t="n">
-        <v>6987268</v>
+        <v>6987113</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3040,7 +3040,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920143</v>
+        <v>125920942</v>
       </c>
       <c r="B22" t="n">
         <v>57651</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448215</v>
+        <v>448197</v>
       </c>
       <c r="R22" t="n">
-        <v>6987268</v>
+        <v>6987113</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125920942</v>
+        <v>125920143</v>
       </c>
       <c r="B23" t="n">
         <v>57651</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448197</v>
+        <v>448215</v>
       </c>
       <c r="R23" t="n">
-        <v>6987113</v>
+        <v>6987268</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3373,7 +3373,7 @@
         <v>125902826</v>
       </c>
       <c r="B25" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3043,7 +3043,7 @@
         <v>125920942</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>125920143</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>125920350</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>125902826</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3043,7 +3043,7 @@
         <v>125920942</v>
       </c>
       <c r="B22" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>125920143</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>125920350</v>
       </c>
       <c r="B24" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>125902826</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3040,7 +3040,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920942</v>
+        <v>125920143</v>
       </c>
       <c r="B22" t="n">
         <v>57656</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448197</v>
+        <v>448215</v>
       </c>
       <c r="R22" t="n">
-        <v>6987113</v>
+        <v>6987268</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125920143</v>
+        <v>125920942</v>
       </c>
       <c r="B23" t="n">
         <v>57656</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448215</v>
+        <v>448197</v>
       </c>
       <c r="R23" t="n">
-        <v>6987268</v>
+        <v>6987113</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3040,7 +3040,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125920143</v>
+        <v>125920942</v>
       </c>
       <c r="B22" t="n">
         <v>57656</v>
@@ -3083,10 +3083,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448215</v>
+        <v>448197</v>
       </c>
       <c r="R22" t="n">
-        <v>6987268</v>
+        <v>6987113</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3150,7 +3150,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125920942</v>
+        <v>125920143</v>
       </c>
       <c r="B23" t="n">
         <v>57656</v>
@@ -3193,10 +3193,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448197</v>
+        <v>448215</v>
       </c>
       <c r="R23" t="n">
-        <v>6987113</v>
+        <v>6987268</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -3043,7 +3043,7 @@
         <v>125920942</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>125920143</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>125920350</v>
       </c>
       <c r="B24" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>125902826</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89591250</v>
+        <v>89591055</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447957.0026399372</v>
+        <v>447081</v>
       </c>
       <c r="R2" t="n">
-        <v>6988806.973930147</v>
+        <v>6988230</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89591050</v>
+        <v>89591251</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447080.9513385269</v>
+        <v>447737</v>
       </c>
       <c r="R3" t="n">
-        <v>6988229.848174844</v>
+        <v>6989265</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +844,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89591246</v>
+        <v>89591050</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447923.9309750172</v>
+        <v>447081</v>
       </c>
       <c r="R4" t="n">
-        <v>6988786.161709175</v>
+        <v>6988230</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +945,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89591053</v>
+        <v>89591074</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447080.9513385269</v>
+        <v>447081</v>
       </c>
       <c r="R5" t="n">
-        <v>6988229.848174844</v>
+        <v>6988230</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,19 +1046,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89591251</v>
+        <v>89591057</v>
       </c>
       <c r="B6" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447737.0109189358</v>
+        <v>447081</v>
       </c>
       <c r="R6" t="n">
-        <v>6989264.995570552</v>
+        <v>6988230</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,19 +1147,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,15 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89591057</v>
+        <v>120787960</v>
       </c>
       <c r="B7" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,37 +1191,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gräftåvallen N, Jmt</t>
+          <t>Skrovellav , Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447080.9513385269</v>
+        <v>447939</v>
       </c>
       <c r="R7" t="n">
-        <v>6988229.848174844</v>
+        <v>6987862</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1325,22 +1248,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,59 +1272,51 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mona Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89591055</v>
+        <v>89591246</v>
       </c>
       <c r="B8" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1326,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447080.9513385269</v>
+        <v>447924</v>
       </c>
       <c r="R8" t="n">
-        <v>6988229.848174844</v>
+        <v>6988786</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,19 +1359,9 @@
           <t>2020-09-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-09-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1487,15 +1392,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89591074</v>
+        <v>120787989</v>
       </c>
       <c r="B9" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1503,37 +1403,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gräftåvallen N, Jmt</t>
+          <t>Lunglav, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447080.9513385269</v>
+        <v>448192</v>
       </c>
       <c r="R9" t="n">
-        <v>6988229.848174844</v>
+        <v>6988391</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,22 +1460,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-09-02</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,37 +1484,29 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Mona Olsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Erland Lindblad</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
-        </is>
-      </c>
+          <t>Mona Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89735735</v>
+        <v>125902826</v>
       </c>
       <c r="B10" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1619,35 +1514,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gräftåvadet, Jmt</t>
+          <t>BERG DÖRRSÅDALEN 1:2, Gräftåvallen, Oviken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448852.3409211119</v>
+        <v>448621</v>
       </c>
       <c r="R10" t="n">
-        <v>6986088.125339356</v>
+        <v>6987672</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1674,22 +1571,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-12-22</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,18 +1585,19 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tor Hansson Frank</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1719,12 +1607,7 @@
         <v>91332150</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447834.1586831671</v>
+        <v>447834</v>
       </c>
       <c r="R11" t="n">
-        <v>6987554.098848508</v>
+        <v>6987554</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1845,15 +1728,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120787872</v>
+        <v>120787498</v>
       </c>
       <c r="B12" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448076</v>
+        <v>448095</v>
       </c>
       <c r="R12" t="n">
-        <v>6987946</v>
+        <v>6988078</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1924,7 +1802,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1812,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1966,15 +1844,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120787960</v>
+        <v>120787799</v>
       </c>
       <c r="B13" t="n">
-        <v>79680</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,37 +1855,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skrovellav , Jmt</t>
+          <t>Ringhack, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447939</v>
+        <v>448452</v>
       </c>
       <c r="R13" t="n">
-        <v>6987862</v>
+        <v>6988269</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2057,13 +1931,17 @@
           <t>11:00</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2082,15 +1960,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120787930</v>
+        <v>120787804</v>
       </c>
       <c r="B14" t="n">
-        <v>90705</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2098,37 +1971,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Granticka, Jmt</t>
+          <t>Ringhack, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448355</v>
+        <v>448456</v>
       </c>
       <c r="R14" t="n">
-        <v>6987955</v>
+        <v>6988109</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2173,13 +2047,17 @@
           <t>11:00</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2201,12 +2079,7 @@
         <v>120787813</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2322,12 +2195,7 @@
         <v>120787821</v>
       </c>
       <c r="B16" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2443,12 +2311,7 @@
         <v>120787844</v>
       </c>
       <c r="B17" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2561,15 +2424,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120787498</v>
+        <v>120787872</v>
       </c>
       <c r="B18" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2605,10 +2463,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>448095</v>
+        <v>448076</v>
       </c>
       <c r="R18" t="n">
-        <v>6988078</v>
+        <v>6987946</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2640,7 +2498,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2650,7 +2508,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2685,12 +2543,7 @@
         <v>120787891</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2803,15 +2656,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120787942</v>
+        <v>125920143</v>
       </c>
       <c r="B20" t="n">
-        <v>90705</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2819,40 +2667,45 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Granticka , Jmt</t>
+          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448199</v>
+        <v>448215</v>
       </c>
       <c r="R20" t="n">
-        <v>6988165</v>
+        <v>6987268</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2876,22 +2729,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2900,34 +2748,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mona Olsson</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mona Olsson</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120787804</v>
+        <v>125920350</v>
       </c>
       <c r="B21" t="n">
-        <v>57348</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2955,21 +2797,25 @@
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ringhack, Jmt</t>
+          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448456</v>
+        <v>448494</v>
       </c>
       <c r="R21" t="n">
-        <v>6988109</v>
+        <v>6987154</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2993,22 +2839,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3028,12 +2864,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mona Olsson</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mona Olsson</t>
+          <t>Tomas Wiltén</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3043,7 +2879,7 @@
         <v>125920942</v>
       </c>
       <c r="B22" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3147,327 +2983,6 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>125920143</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>448215</v>
-      </c>
-      <c r="R23" t="n">
-        <v>6987268</v>
-      </c>
-      <c r="S23" t="n">
-        <v>25</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Tomas Wiltén</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Tomas Wiltén</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>125920350</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57657</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>BERG DÖRRSÅDALEN 1:2, Jmt</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>448494</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6987154</v>
-      </c>
-      <c r="S24" t="n">
-        <v>25</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Tomas Wiltén</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Tomas Wiltén</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>125902826</v>
-      </c>
-      <c r="B25" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>BERG DÖRRSÅDALEN 1:2, Gräftåvallen, Oviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>448621</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6987672</v>
-      </c>
-      <c r="S25" t="n">
-        <v>25</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Berg</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Oviken</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2025-06-10</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Tomas Wiltén</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Tomas Wiltén</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20809-2025 artfynd.xlsx
+++ b/artfynd/A 20809-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89591055</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89591251</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89591050</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89591074</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1175,6 +1200,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89591057</t>
         </is>
       </c>
     </row>
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787960</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Kontinuitetsskogar och skogar med höga naturvärden ovan och i nära anslutning till fjällnära gränsen</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89591246</t>
         </is>
       </c>
     </row>
@@ -1500,6 +1540,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787989</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1601,6 +1646,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125902826</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91332150</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1841,6 +1896,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787498</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787799</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2073,6 +2138,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787804</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2189,6 +2259,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787813</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2305,6 +2380,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787821</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2421,6 +2501,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787844</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2537,6 +2622,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787872</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2653,6 +2743,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120787891</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2763,6 +2858,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920143</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2873,6 +2973,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920350</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2983,8 +3088,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125920942</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>